--- a/Plotting/Results_excels/production_shares_olefins_Scope1-3_FPO.xlsx
+++ b/Plotting/Results_excels/production_shares_olefins_Scope1-3_FPO.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,6 +483,27 @@
       </c>
       <c r="I1" s="1" t="n"/>
       <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Iteration_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Iteration_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Iteration_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="n"/>
+      <c r="S1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -535,11 +556,56 @@
           <t>2050</t>
         </is>
       </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Conventional</t>
+          <t>Conventional (fossil)</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -567,13 +633,40 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Carbon Capture</t>
+          <t>Conventional (fossil) with CC</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -601,6 +694,33 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -620,22 +740,49 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1401265.181013477</v>
+        <v>1401265.181013577</v>
       </c>
       <c r="F6" t="n">
-        <v>601941.0560588671</v>
+        <v>599911.1983811827</v>
       </c>
       <c r="G6" t="n">
-        <v>220300.6047496275</v>
+        <v>218275.37673335</v>
       </c>
       <c r="H6" t="n">
-        <v>1401265.181013555</v>
+        <v>1654577.419078082</v>
       </c>
       <c r="I6" t="n">
-        <v>603301.943119394</v>
+        <v>511316.4752069731</v>
       </c>
       <c r="J6" t="n">
-        <v>221658.387924635</v>
+        <v>327497.3005624756</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1654495.849593349</v>
+      </c>
+      <c r="L6" t="n">
+        <v>510329.7565155794</v>
+      </c>
+      <c r="M6" t="n">
+        <v>327496.7010239341</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1660923.006050798</v>
+      </c>
+      <c r="O6" t="n">
+        <v>709429.5499024262</v>
+      </c>
+      <c r="P6" t="n">
+        <v>327543.9408587801</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1656801.512260815</v>
+      </c>
+      <c r="R6" t="n">
+        <v>512165.7261827416</v>
+      </c>
+      <c r="S6" t="n">
+        <v>327513.6477285263</v>
       </c>
     </row>
     <row r="7">
@@ -671,6 +818,33 @@
       <c r="J7" t="n">
         <v>0</v>
       </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -688,22 +862,49 @@
         <v>1205602.936901779</v>
       </c>
       <c r="E8" t="n">
-        <v>5.632199962251493e-09</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>833772.8317698874</v>
+        <v>835948.5047002221</v>
       </c>
       <c r="G8" t="n">
-        <v>895449.9642983549</v>
+        <v>898147.9214748184</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>830721.5900870636</v>
+        <v>982844.0272473533</v>
       </c>
       <c r="J8" t="n">
-        <v>893641.1601385501</v>
+        <v>752645.2566738896</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>982812.0070056837</v>
+      </c>
+      <c r="M8" t="n">
+        <v>752646.055364063</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>816295.8721399774</v>
+      </c>
+      <c r="P8" t="n">
+        <v>752583.1236593793</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>983717.0988657931</v>
+      </c>
+      <c r="S8" t="n">
+        <v>752623.4793958906</v>
       </c>
     </row>
     <row r="9">
@@ -722,22 +923,49 @@
         <v>-1.136217926629919e-10</v>
       </c>
       <c r="E9" t="n">
-        <v>316335.4517645898</v>
+        <v>316335.4517647075</v>
       </c>
       <c r="F9" t="n">
-        <v>-6.255461908579836e-11</v>
+        <v>-6.252214811315127e-11</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.335831718417106e-10</v>
+        <v>-6.319312228100514e-11</v>
       </c>
       <c r="H9" t="n">
-        <v>316335.4517647323</v>
+        <v>63075.75253474692</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>74485.82018329554</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.336833811490258e-10</v>
+        <v>3.359748570954768e-08</v>
+      </c>
+      <c r="K9" t="n">
+        <v>63157.30510138743</v>
+      </c>
+      <c r="L9" t="n">
+        <v>75516.94831064175</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-9.169578123541005e-11</v>
+      </c>
+      <c r="N9" t="n">
+        <v>56731.48168369583</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.128649688751616e-11</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-1.485213028294221e-08</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>60852.12064545505</v>
+      </c>
+      <c r="R9" t="n">
+        <v>71857.68785582769</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-9.23055853341686e-11</v>
       </c>
     </row>
     <row r="10">
@@ -759,19 +987,46 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>281720.9592051049</v>
+        <v>281574.7229447911</v>
       </c>
       <c r="G10" t="n">
-        <v>601605.122929297</v>
+        <v>600931.9737218219</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>283411.5960854487</v>
+        <v>148769.7281868651</v>
       </c>
       <c r="J10" t="n">
-        <v>602056.4255283808</v>
+        <v>637235.3681296469</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>148757.134339818</v>
+      </c>
+      <c r="M10" t="n">
+        <v>637235.1688536991</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>191731.718901282</v>
+      </c>
+      <c r="P10" t="n">
+        <v>637250.8705214455</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>149675.7140610712</v>
+      </c>
+      <c r="S10" t="n">
+        <v>637240.8016320763</v>
       </c>
     </row>
     <row r="11">
@@ -790,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>5.699881611755716e-08</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -805,6 +1060,33 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.103221667151047e-08</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -841,6 +1123,33 @@
       <c r="J12" t="n">
         <v>0</v>
       </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -875,6 +1184,33 @@
       <c r="J13" t="n">
         <v>0</v>
       </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -909,6 +1245,33 @@
       <c r="J14" t="n">
         <v>0</v>
       </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -943,6 +1306,33 @@
       <c r="J15" t="n">
         <v>0</v>
       </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -977,12 +1367,42 @@
       <c r="J16" t="n">
         <v>0</v>
       </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="6">
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="B1:D1"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="Q1:S1"/>
     <mergeCell ref="E1:G1"/>
+    <mergeCell ref="K1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
